--- a/src/test/resources/testdata/Modules/10_MyHealthBenefits/MyHealthBenefits/01_MyHealthBenefitsTest.xlsx
+++ b/src/test/resources/testdata/Modules/10_MyHealthBenefits/MyHealthBenefits/01_MyHealthBenefitsTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\10_MyHealthBenefits\MyHealthBenefits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B20365-02C6-4B99-8BA1-672B640FD313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843832DD-0863-45C4-B97F-CF5C4A1B2365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="259">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -3473,6 +3473,32 @@
 clickon_mailicon
 clickon_mailicon
 verify_welcometomail_text</t>
+  </si>
+  <si>
+    <t>INFLUENCER_MOBILENO</t>
+  </si>
+  <si>
+    <t>OTP</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>6277272828</t>
+  </si>
+  <si>
+    <t>clickonskipbtnofinsurancewindow
+profile_clickon_showprofile
+clickon_signout
+clickon_signout_yesbtn
+enter_loginmobilenumber
+hidekeyboard
+clickongetotpbtn
+enterotp
+hidekeyboard
+clickonotpsubmitbtn
+open_myhealthbenefitsmenu
+verify_pagetitle</t>
   </si>
 </sst>
 </file>
@@ -4405,7 +4431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" style="2" customWidth="1"/>
@@ -4413,16 +4439,18 @@
     <col min="3" max="3" width="21.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75.08984375" style="7" customWidth="1"/>
     <col min="5" max="5" width="40.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="45.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.90625" style="2"/>
+    <col min="6" max="6" width="34.54296875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="45.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
@@ -4439,25 +4467,31 @@
         <v>3</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="174" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -4471,20 +4505,26 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+        <v>258</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>256</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -4503,15 +4543,17 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="1" t="s">
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -4530,15 +4572,17 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="1" t="s">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -4557,15 +4601,17 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="1" t="s">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -4584,15 +4630,17 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="1" t="s">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -4611,15 +4659,17 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="1" t="s">
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -4638,15 +4688,17 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="1" t="s">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -4665,15 +4717,17 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="1" t="s">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -4692,15 +4746,17 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="1" t="s">
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -4719,15 +4775,17 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="1" t="s">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -4746,15 +4804,17 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="1" t="s">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -4773,15 +4833,17 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="1" t="s">
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -4800,15 +4862,17 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="1" t="s">
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -4827,15 +4891,17 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="1" t="s">
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="M15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
@@ -4854,15 +4920,17 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="1" t="s">
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
@@ -4881,15 +4949,17 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="1" t="s">
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
@@ -4908,15 +4978,17 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="1" t="s">
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
@@ -4935,15 +5007,17 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="1" t="s">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -4962,15 +5036,17 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="1" t="s">
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
@@ -4989,15 +5065,17 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="1" t="s">
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
@@ -5016,15 +5094,17 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="1" t="s">
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>9</v>
       </c>
@@ -5043,15 +5123,17 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="1" t="s">
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
@@ -5070,15 +5152,17 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="1" t="s">
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
@@ -5097,15 +5181,17 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="1" t="s">
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="M25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
@@ -5124,15 +5210,17 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="1" t="s">
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
@@ -5151,15 +5239,17 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="1" t="s">
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>9</v>
       </c>
@@ -5178,15 +5268,17 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="1" t="s">
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>9</v>
       </c>
@@ -5202,19 +5294,21 @@
       <c r="E29" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="1" t="s">
+      <c r="J29" s="1"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="M29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>9</v>
       </c>
@@ -5231,19 +5325,21 @@
         <v>237</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="1" t="s">
+      <c r="J30" s="1"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>9</v>
       </c>
@@ -5260,19 +5356,21 @@
         <v>214</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="1"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>9</v>
       </c>
@@ -5291,15 +5389,17 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="1" t="s">
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="145" x14ac:dyDescent="0.35">
+      <c r="M32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="145" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>9</v>
       </c>
@@ -5315,24 +5415,26 @@
       <c r="E33" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="J33" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I33" s="5"/>
-      <c r="J33" s="1" t="s">
+      <c r="K33" s="5"/>
+      <c r="L33" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="M33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>9</v>
       </c>
@@ -5351,15 +5453,17 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="1" t="s">
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M34" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>9</v>
       </c>
@@ -5378,15 +5482,17 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="1" t="s">
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M35" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>9</v>
       </c>
@@ -5405,15 +5511,17 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="1" t="s">
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M36" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>9</v>
       </c>
@@ -5432,15 +5540,17 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="1" t="s">
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M37" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>9</v>
       </c>
@@ -5459,15 +5569,17 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="1" t="s">
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>9</v>
       </c>
@@ -5486,15 +5598,17 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="1" t="s">
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M39" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>9</v>
       </c>
@@ -5513,15 +5627,17 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="1" t="s">
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M40" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>9</v>
       </c>
@@ -5540,15 +5656,17 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="1" t="s">
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M41" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>9</v>
       </c>
@@ -5567,15 +5685,17 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="1" t="s">
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="M42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>9</v>
       </c>
@@ -5594,15 +5714,17 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M43" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>9</v>
       </c>
@@ -5621,15 +5743,17 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="1" t="s">
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>9</v>
       </c>
@@ -5648,15 +5772,17 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="1" t="s">
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M45" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>9</v>
       </c>
@@ -5672,22 +5798,22 @@
       <c r="E46" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="H46" s="1"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="1" t="s">
+      <c r="J46" s="1"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M46" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>9</v>
       </c>
@@ -5703,20 +5829,20 @@
       <c r="E47" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1"/>
+      <c r="I47" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H47" s="1"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="1" t="s">
+      <c r="J47" s="1"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M47" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>9</v>
       </c>
@@ -5732,18 +5858,18 @@
       <c r="E48" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="2" t="s">
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M48" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>9</v>
       </c>
@@ -5759,18 +5885,18 @@
       <c r="E49" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
       <c r="H49" s="1"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="1" t="s">
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="145" x14ac:dyDescent="0.35">
+      <c r="M49" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="145" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>9</v>
       </c>
@@ -5786,24 +5912,24 @@
       <c r="E50" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="J50" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="I50" s="5"/>
-      <c r="J50" s="1" t="s">
+      <c r="K50" s="5"/>
+      <c r="L50" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="M50" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>9</v>
       </c>
@@ -5819,15 +5945,15 @@
       <c r="E51" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I51" s="5"/>
-      <c r="J51" s="1" t="s">
+      <c r="K51" s="5"/>
+      <c r="L51" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M51" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>9</v>
       </c>
@@ -5843,18 +5969,18 @@
       <c r="E52" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="1" t="s">
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M52" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>9</v>
       </c>
@@ -5870,18 +5996,18 @@
       <c r="E53" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="1" t="s">
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M53" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>9</v>
       </c>
@@ -5897,18 +6023,18 @@
       <c r="E54" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="1" t="s">
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M54" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>9</v>
       </c>
@@ -5924,18 +6050,18 @@
       <c r="E55" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
       <c r="H55" s="1"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="1" t="s">
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M55" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>9</v>
       </c>
@@ -5951,18 +6077,18 @@
       <c r="E56" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
       <c r="H56" s="1"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="1" t="s">
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M56" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>9</v>
       </c>
@@ -5978,18 +6104,18 @@
       <c r="E57" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
       <c r="H57" s="1"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="1" t="s">
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M57" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>9</v>
       </c>
@@ -6005,18 +6131,18 @@
       <c r="E58" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="1" t="s">
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M58" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>9</v>
       </c>
@@ -6032,18 +6158,18 @@
       <c r="E59" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="1" t="s">
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M59" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>9</v>
       </c>
@@ -6059,18 +6185,18 @@
       <c r="E60" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
       <c r="H60" s="1"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="1" t="s">
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M60" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>9</v>
       </c>
@@ -6086,18 +6212,18 @@
       <c r="E61" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="1" t="s">
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M61" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>9</v>
       </c>
@@ -6113,18 +6239,18 @@
       <c r="E62" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
       <c r="H62" s="1"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="1" t="s">
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M62" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>9</v>
       </c>
@@ -6140,18 +6266,18 @@
       <c r="E63" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="1" t="s">
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M63" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>9</v>
       </c>
@@ -6167,18 +6293,18 @@
       <c r="E64" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
       <c r="H64" s="1"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="1" t="s">
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M64" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>9</v>
       </c>
@@ -6194,18 +6320,18 @@
       <c r="E65" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="1" t="s">
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K65" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M65" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>9</v>
       </c>
@@ -6221,18 +6347,18 @@
       <c r="E66" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
       <c r="H66" s="1"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="1" t="s">
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M66" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>9</v>
       </c>
@@ -6248,22 +6374,22 @@
       <c r="E67" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="H67" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="I67" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="H67" s="1"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="1" t="s">
+      <c r="J67" s="1"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M67" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>9</v>
       </c>
@@ -6279,20 +6405,20 @@
       <c r="E68" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1" t="s">
+      <c r="H68" s="1"/>
+      <c r="I68" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="H68" s="1"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="1" t="s">
+      <c r="J68" s="1"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M68" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>9</v>
       </c>
@@ -6308,18 +6434,18 @@
       <c r="E69" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
       <c r="H69" s="1"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="2" t="s">
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="M69" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>9</v>
       </c>
@@ -6335,18 +6461,18 @@
       <c r="E70" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
       <c r="H70" s="1"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="2" t="s">
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K70" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="M70" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>9</v>
       </c>
@@ -6362,15 +6488,15 @@
       <c r="E71" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="I71" s="5"/>
-      <c r="J71" s="1" t="s">
+      <c r="K71" s="5"/>
+      <c r="L71" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K71" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="232" x14ac:dyDescent="0.35">
+      <c r="M71" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="232" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>9</v>
       </c>
@@ -6386,20 +6512,20 @@
       <c r="E72" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="H72" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="I72" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="J72" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I72" s="5"/>
-      <c r="J72" s="1" t="s">
+      <c r="K72" s="5"/>
+      <c r="L72" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="M72" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/src/test/resources/testdata/Modules/10_MyHealthBenefits/MyHealthBenefits/01_MyHealthBenefitsTest.xlsx
+++ b/src/test/resources/testdata/Modules/10_MyHealthBenefits/MyHealthBenefits/01_MyHealthBenefitsTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\10_MyHealthBenefits\MyHealthBenefits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843832DD-0863-45C4-B97F-CF5C4A1B2365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CF64F4-D9B2-4EA0-8A8B-93C244B0A0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>

--- a/src/test/resources/testdata/Modules/10_MyHealthBenefits/MyHealthBenefits/01_MyHealthBenefitsTest.xlsx
+++ b/src/test/resources/testdata/Modules/10_MyHealthBenefits/MyHealthBenefits/01_MyHealthBenefitsTest.xlsx
@@ -1,24 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\10_MyHealthBenefits\MyHealthBenefits\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2BF7D8-2C08-47C9-ADC3-BEEE99717A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="TestCases"/>
-    <sheet r:id="rId2" sheetId="2" name="Sheet1"/>
+    <sheet name="TestCases" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet1!$A$1:$K$1</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="261">
   <si>
     <t>INFLUENCER_ACCOUNT</t>
   </si>
@@ -3261,13 +3267,18 @@
   <si>
     <t>IndusInd General Insurance logo</t>
   </si>
+  <si>
+    <t>navigatebackto_myhealthpage
+clickon_teleconsulting_arrow
+clickon_mailicon_try
+verify_welcometomail_text</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3278,7 +3289,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -3294,6 +3305,34 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3304,17 +3343,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0070c0"/>
+        <fgColor rgb="FF0070C0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffff00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffffff"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -3352,77 +3391,90 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3433,10 +3485,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -3474,71 +3526,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3566,7 +3618,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -3589,11 +3641,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -3602,13 +3654,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -3618,7 +3670,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -3627,7 +3679,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -3636,7 +3688,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -3644,10 +3696,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -3712,77 +3764,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="18" width="12.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="19" width="20.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="19" width="21.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="20" width="75.14785714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="19" width="40.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="18" width="34.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="18" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="19" width="16.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="18" width="18.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="19" width="18.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="19" width="15.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="18" width="45.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="19" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="20.90625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.36328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="122.36328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.453125" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.81640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.36328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.54296875" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.54296875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.08984375" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7265625" style="17"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
-      <c r="A2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="16" t="s">
+    <row r="2" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -3804,134 +3857,134 @@
       <c r="L2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
-      <c r="A3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="M2" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="4" t="s">
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="M3" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="4" t="s">
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="M4" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="4" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
-      <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="M5" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="4" t="s">
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
-      <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="16" t="s">
+      <c r="M6" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -3940,27 +3993,27 @@
       <c r="E7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="4" t="s">
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="M7" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="10" t="s">
@@ -3969,27 +4022,27 @@
       <c r="E8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="4" t="s">
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="M8" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3998,27 +4051,27 @@
       <c r="E9" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="4" t="s">
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="M9" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>43</v>
       </c>
       <c r="D10" s="10" t="s">
@@ -4027,114 +4080,114 @@
       <c r="E10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="4" t="s">
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
-      <c r="A11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="M10" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="4" t="s">
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="M11" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>51</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="4" t="s">
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M12" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
-      <c r="A13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="M12" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="4" t="s">
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="M13" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
-      <c r="A14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="M13" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>58</v>
       </c>
       <c r="D14" s="10" t="s">
@@ -4143,27 +4196,27 @@
       <c r="E14" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="4" t="s">
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="M14" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
-      <c r="A15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="16" t="s">
+      <c r="M14" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>62</v>
       </c>
       <c r="D15" s="10" t="s">
@@ -4172,56 +4225,56 @@
       <c r="E15" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="4" t="s">
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="M15" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
-      <c r="A16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="16" t="s">
+      <c r="M15" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>66</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="M16" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
-      <c r="A17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="16" t="s">
+      <c r="M16" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>69</v>
       </c>
       <c r="D17" s="10" t="s">
@@ -4230,143 +4283,143 @@
       <c r="E17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="4" t="s">
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="M17" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
-      <c r="A18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="M17" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>73</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="4" t="s">
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="M18" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
-      <c r="A19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="M18" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>77</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="4" t="s">
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M19" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
-      <c r="A20" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="M19" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>80</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="4" t="s">
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="M20" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
-      <c r="A21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="M20" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>84</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="4" t="s">
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="M21" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
-      <c r="A22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="M21" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>88</v>
       </c>
       <c r="D22" s="10" t="s">
@@ -4375,27 +4428,27 @@
       <c r="E22" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="4" t="s">
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="M22" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
-      <c r="A23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="M22" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>92</v>
       </c>
       <c r="D23" s="10" t="s">
@@ -4404,27 +4457,27 @@
       <c r="E23" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="4" t="s">
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="M23" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
-      <c r="A24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="M23" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>96</v>
       </c>
       <c r="D24" s="10" t="s">
@@ -4433,27 +4486,27 @@
       <c r="E24" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="4" t="s">
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="M24" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
-      <c r="A25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="M24" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>100</v>
       </c>
       <c r="D25" s="10" t="s">
@@ -4462,27 +4515,27 @@
       <c r="E25" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="4" t="s">
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="M25" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
-      <c r="A26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="M25" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>103</v>
       </c>
       <c r="D26" s="10" t="s">
@@ -4491,56 +4544,56 @@
       <c r="E26" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="4" t="s">
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="M26" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
-      <c r="A27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="M26" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="20" t="s">
         <v>107</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="4" t="s">
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="M27" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
-      <c r="A28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="16" t="s">
+      <c r="M27" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="20" t="s">
         <v>111</v>
       </c>
       <c r="D28" s="10" t="s">
@@ -4549,27 +4602,27 @@
       <c r="E28" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="4" t="s">
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M28" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
-      <c r="A29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="16" t="s">
+      <c r="M28" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="20" t="s">
         <v>115</v>
       </c>
       <c r="D29" s="10" t="s">
@@ -4578,29 +4631,28 @@
       <c r="E29" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="5" t="s">
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="4" t="s">
+      <c r="J29" s="21"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="M29" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
-      <c r="A30" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="M29" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="20" t="s">
         <v>120</v>
       </c>
       <c r="D30" s="10" t="s">
@@ -4609,29 +4661,29 @@
       <c r="E30" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="4" t="s">
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="J30" s="11"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="4" t="s">
+      <c r="J30" s="21"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="M30" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
-      <c r="A31" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="M30" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="20" t="s">
         <v>125</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -4640,29 +4692,29 @@
       <c r="E31" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="4" t="s">
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="J31" s="11"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="14" t="s">
+      <c r="J31" s="21"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="M31" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
-      <c r="A32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="M31" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="20" t="s">
         <v>130</v>
       </c>
       <c r="D32" s="10" t="s">
@@ -4671,27 +4723,27 @@
       <c r="E32" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="4" t="s">
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="M32" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
-      <c r="A33" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="16" t="s">
+      <c r="M32" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="20" t="s">
         <v>133</v>
       </c>
       <c r="D33" s="10" t="s">
@@ -4700,33 +4752,33 @@
       <c r="E33" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="5" t="s">
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="K33" s="12"/>
-      <c r="L33" s="4" t="s">
+      <c r="K33" s="22"/>
+      <c r="L33" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="M33" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
-      <c r="A34" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="M33" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="20" t="s">
         <v>137</v>
       </c>
       <c r="D34" s="10" t="s">
@@ -4735,143 +4787,143 @@
       <c r="E34" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="4" t="s">
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="M34" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
-      <c r="A35" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="16" t="s">
+      <c r="M34" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="20" t="s">
         <v>141</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="4" t="s">
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="M35" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
-      <c r="A36" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="M35" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="20" t="s">
         <v>144</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="4" t="s">
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M36" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
-      <c r="A37" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="16" t="s">
+      <c r="M36" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>146</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="4" t="s">
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="M37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
-      <c r="A38" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="16" t="s">
+      <c r="M37" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>149</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="4" t="s">
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="M38" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
-      <c r="A39" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="M38" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>152</v>
       </c>
       <c r="D39" s="10" t="s">
@@ -4880,27 +4932,27 @@
       <c r="E39" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="4" t="s">
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="M39" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
-      <c r="A40" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="16" t="s">
+      <c r="M39" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>154</v>
       </c>
       <c r="D40" s="10" t="s">
@@ -4909,27 +4961,27 @@
       <c r="E40" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="4" t="s">
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="M40" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
-      <c r="A41" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="M40" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>157</v>
       </c>
       <c r="D41" s="10" t="s">
@@ -4938,27 +4990,27 @@
       <c r="E41" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="4" t="s">
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="M41" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
-      <c r="A42" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="16" t="s">
+      <c r="M41" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>160</v>
       </c>
       <c r="D42" s="10" t="s">
@@ -4967,27 +5019,27 @@
       <c r="E42" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="4" t="s">
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="M42" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
-      <c r="A43" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="16" t="s">
+      <c r="M42" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="20" t="s">
         <v>163</v>
       </c>
       <c r="D43" s="10" t="s">
@@ -4996,56 +5048,56 @@
       <c r="E43" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="4" t="s">
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="M43" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
-      <c r="A44" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="16" t="s">
+      <c r="M43" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="20" t="s">
         <v>166</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="4" t="s">
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="M44" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
-      <c r="A45" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="16" t="s">
+      <c r="M44" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="20" t="s">
         <v>168</v>
       </c>
       <c r="D45" s="10" t="s">
@@ -5054,27 +5106,27 @@
       <c r="E45" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="4" t="s">
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M45" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
-      <c r="A46" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="16" t="s">
+      <c r="M45" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="20" t="s">
         <v>170</v>
       </c>
       <c r="D46" s="10" t="s">
@@ -5083,31 +5135,29 @@
       <c r="E46" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="I46" s="4" t="s">
+      <c r="I46" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="J46" s="11"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="4" t="s">
+      <c r="J46" s="21"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="M46" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
-      <c r="A47" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="16" t="s">
+      <c r="M46" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="20" t="s">
         <v>174</v>
       </c>
       <c r="D47" s="10" t="s">
@@ -5116,29 +5166,27 @@
       <c r="E47" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="4" t="s">
+      <c r="H47" s="21"/>
+      <c r="I47" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="J47" s="11"/>
-      <c r="K47" s="12"/>
-      <c r="L47" s="4" t="s">
+      <c r="J47" s="21"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="M47" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
-      <c r="A48" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="16" t="s">
+      <c r="M47" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>177</v>
       </c>
       <c r="D48" s="10" t="s">
@@ -5147,27 +5195,25 @@
       <c r="E48" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="14" t="s">
+      <c r="H48" s="21"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="21"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="M48" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
-      <c r="A49" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="16" t="s">
+      <c r="M48" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="20" t="s">
         <v>181</v>
       </c>
       <c r="D49" s="10" t="s">
@@ -5176,27 +5222,25 @@
       <c r="E49" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="12"/>
-      <c r="L49" s="4" t="s">
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="M49" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
-      <c r="A50" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="16" t="s">
+      <c r="M49" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="20" t="s">
         <v>183</v>
       </c>
       <c r="D50" s="10" t="s">
@@ -5205,33 +5249,31 @@
       <c r="E50" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="5" t="s">
+      <c r="H50" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="I50" s="4" t="s">
+      <c r="I50" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="J50" s="5" t="s">
+      <c r="J50" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="K50" s="12"/>
-      <c r="L50" s="4" t="s">
+      <c r="K50" s="22"/>
+      <c r="L50" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="M50" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
-      <c r="A51" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="16" t="s">
+      <c r="M50" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="20" t="s">
         <v>186</v>
       </c>
       <c r="D51" s="10" t="s">
@@ -5240,143 +5282,130 @@
       <c r="E51" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="4" t="s">
+      <c r="K51" s="22"/>
+      <c r="L51" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="M51" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
-      <c r="A52" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="16" t="s">
+      <c r="M51" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="20" t="s">
         <v>190</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="4" t="s">
+      <c r="H52" s="21"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="M52" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
-      <c r="A53" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="16" t="s">
+      <c r="M52" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="20" t="s">
         <v>193</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="12"/>
-      <c r="L53" s="4" t="s">
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M53" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
-      <c r="A54" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="16" t="s">
+      <c r="M53" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="4" t="s">
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="22"/>
+      <c r="L54" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="M54" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
-      <c r="A55" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="16" t="s">
+      <c r="M54" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="20" t="s">
         <v>197</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="12"/>
-      <c r="L55" s="4" t="s">
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="M55" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
-      <c r="A56" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="16" t="s">
+      <c r="M55" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="20" t="s">
         <v>200</v>
       </c>
       <c r="D56" s="10" t="s">
@@ -5385,27 +5414,25 @@
       <c r="E56" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="4" t="s">
+      <c r="H56" s="21"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="21"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="M56" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
-      <c r="A57" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="16" t="s">
+      <c r="M56" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="20" t="s">
         <v>202</v>
       </c>
       <c r="D57" s="10" t="s">
@@ -5414,27 +5441,25 @@
       <c r="E57" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="4" t="s">
+      <c r="H57" s="21"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="M57" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
-      <c r="A58" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="16" t="s">
+      <c r="M57" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="20" t="s">
         <v>206</v>
       </c>
       <c r="D58" s="10" t="s">
@@ -5443,27 +5468,25 @@
       <c r="E58" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="12"/>
-      <c r="L58" s="4" t="s">
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="M58" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
-      <c r="A59" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="16" t="s">
+      <c r="M58" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="20" t="s">
         <v>210</v>
       </c>
       <c r="D59" s="10" t="s">
@@ -5472,27 +5495,25 @@
       <c r="E59" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
-      <c r="K59" s="12"/>
-      <c r="L59" s="4" t="s">
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="M59" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
-      <c r="A60" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="16" t="s">
+      <c r="M59" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="20" t="s">
         <v>214</v>
       </c>
       <c r="D60" s="10" t="s">
@@ -5501,27 +5522,25 @@
       <c r="E60" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="12"/>
-      <c r="L60" s="4" t="s">
+      <c r="H60" s="21"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="M60" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
-      <c r="A61" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="16" t="s">
+      <c r="M60" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="20" t="s">
         <v>218</v>
       </c>
       <c r="D61" s="10" t="s">
@@ -5530,27 +5549,25 @@
       <c r="E61" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="12"/>
-      <c r="L61" s="4" t="s">
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="M61" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
-      <c r="A62" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="16" t="s">
+      <c r="M61" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="20" t="s">
         <v>222</v>
       </c>
       <c r="D62" s="10" t="s">
@@ -5559,27 +5576,25 @@
       <c r="E62" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="12"/>
-      <c r="L62" s="4" t="s">
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="M62" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
-      <c r="A63" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="16" t="s">
+      <c r="M62" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="20" t="s">
         <v>225</v>
       </c>
       <c r="D63" s="10" t="s">
@@ -5588,27 +5603,25 @@
       <c r="E63" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="11"/>
-      <c r="J63" s="11"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="4" t="s">
+      <c r="H63" s="21"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="21"/>
+      <c r="K63" s="22"/>
+      <c r="L63" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="M63" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
-      <c r="A64" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="16" t="s">
+      <c r="M63" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="20" t="s">
         <v>228</v>
       </c>
       <c r="D64" s="10" t="s">
@@ -5617,27 +5630,25 @@
       <c r="E64" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
-      <c r="K64" s="12"/>
-      <c r="L64" s="4" t="s">
+      <c r="H64" s="21"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="M64" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
-      <c r="A65" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="16" t="s">
+      <c r="M64" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="20" t="s">
         <v>231</v>
       </c>
       <c r="D65" s="10" t="s">
@@ -5646,56 +5657,52 @@
       <c r="E65" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="4" t="s">
+      <c r="H65" s="21"/>
+      <c r="I65" s="21"/>
+      <c r="J65" s="21"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="M65" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
-      <c r="A66" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C66" s="16" t="s">
+      <c r="M65" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="20" t="s">
         <v>234</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="12"/>
-      <c r="L66" s="4" t="s">
+      <c r="H66" s="21"/>
+      <c r="I66" s="21"/>
+      <c r="J66" s="21"/>
+      <c r="K66" s="22"/>
+      <c r="L66" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M66" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
-      <c r="A67" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="16" t="s">
+      <c r="M66" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="20" t="s">
         <v>237</v>
       </c>
       <c r="D67" s="10" t="s">
@@ -5704,31 +5711,29 @@
       <c r="E67" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="5" t="s">
+      <c r="H67" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="I67" s="4" t="s">
+      <c r="I67" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="J67" s="11"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="4" t="s">
+      <c r="J67" s="21"/>
+      <c r="K67" s="22"/>
+      <c r="L67" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="M67" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
-      <c r="A68" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="16" t="s">
+      <c r="M67" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="20" t="s">
         <v>239</v>
       </c>
       <c r="D68" s="10" t="s">
@@ -5737,29 +5742,27 @@
       <c r="E68" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="4" t="s">
+      <c r="H68" s="21"/>
+      <c r="I68" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="J68" s="11"/>
-      <c r="K68" s="12"/>
-      <c r="L68" s="4" t="s">
+      <c r="J68" s="21"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="M68" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
-      <c r="A69" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" s="16" t="s">
+      <c r="M68" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="20" t="s">
         <v>242</v>
       </c>
       <c r="D69" s="10" t="s">
@@ -5768,56 +5771,52 @@
       <c r="E69" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="11"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="14" t="s">
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="M69" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
-      <c r="A70" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" s="16" t="s">
+      <c r="M69" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="20" t="s">
         <v>245</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E70" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11"/>
-      <c r="K70" s="12"/>
-      <c r="L70" s="14" t="s">
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="M70" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="33">
-      <c r="A71" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" s="16" t="s">
+      <c r="M70" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="20" t="s">
         <v>248</v>
       </c>
       <c r="D71" s="10" t="s">
@@ -5826,27 +5825,22 @@
       <c r="E71" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="4" t="s">
+      <c r="K71" s="22"/>
+      <c r="L71" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="M71" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="186.75">
-      <c r="A72" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" s="16" t="s">
+      <c r="M71" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="186.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="20" t="s">
         <v>250</v>
       </c>
       <c r="D72" s="10" t="s">
@@ -5855,22 +5849,20 @@
       <c r="E72" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="5" t="s">
+      <c r="H72" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="I72" s="4" t="s">
+      <c r="I72" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="J72" s="5" t="s">
+      <c r="J72" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="K72" s="12"/>
-      <c r="L72" s="4" t="s">
+      <c r="K72" s="22"/>
+      <c r="L72" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="M72" s="5" t="s">
+      <c r="M72" s="10" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5880,27 +5872,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="18" width="12.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="19" width="20.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="19" width="21.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="20" width="75.14785714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="19" width="40.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="19" width="16.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="18" width="18.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="19" width="18.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="19" width="15.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="18" width="45.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="19" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="12.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75.1796875" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="45.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5935,7 +5927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -5962,7 +5954,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -5989,7 +5981,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+    <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -6016,7 +6008,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -6043,7 +6035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row r="6" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -6070,7 +6062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row r="7" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -6097,7 +6089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row r="8" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
@@ -6124,7 +6116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row r="9" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -6151,7 +6143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row r="10" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -6178,7 +6170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row r="11" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -6205,7 +6197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row r="12" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -6232,7 +6224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row r="13" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -6259,7 +6251,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row r="14" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
@@ -6286,7 +6278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row r="15" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
@@ -6313,7 +6305,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
@@ -6340,7 +6332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+    <row r="17" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
@@ -6367,7 +6359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
+    <row r="18" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
@@ -6394,7 +6386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
+    <row r="19" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
@@ -6421,7 +6413,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+    <row r="20" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
@@ -6448,7 +6440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+    <row r="21" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
@@ -6475,7 +6467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+    <row r="22" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
@@ -6502,7 +6494,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
+    <row r="23" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>11</v>
       </c>
@@ -6529,7 +6521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
+    <row r="24" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>11</v>
       </c>
@@ -6556,7 +6548,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
+    <row r="25" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -6583,7 +6575,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+    <row r="26" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>11</v>
       </c>
@@ -6610,7 +6602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+    <row r="27" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>11</v>
       </c>
@@ -6637,7 +6629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+    <row r="28" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>11</v>
       </c>
@@ -6664,7 +6656,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
+    <row r="29" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>11</v>
       </c>
@@ -6683,7 +6675,6 @@
       <c r="F29" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G29" s="13"/>
       <c r="H29" s="11"/>
       <c r="I29" s="12"/>
       <c r="J29" s="4" t="s">
@@ -6693,7 +6684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
+    <row r="30" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>11</v>
       </c>
@@ -6722,7 +6713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
+    <row r="31" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>11</v>
       </c>
@@ -6751,7 +6742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
+    <row r="32" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>11</v>
       </c>
@@ -6778,7 +6769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
+    <row r="33" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>11</v>
       </c>
@@ -6811,7 +6802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
+    <row r="34" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>11</v>
       </c>
@@ -6838,7 +6829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
+    <row r="35" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>11</v>
       </c>
@@ -6865,7 +6856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
+    <row r="36" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>11</v>
       </c>
@@ -6892,7 +6883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
+    <row r="37" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
@@ -6919,7 +6910,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
+    <row r="38" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>11</v>
       </c>
@@ -6946,7 +6937,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
+    <row r="39" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>11</v>
       </c>
@@ -6973,7 +6964,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
+    <row r="40" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>11</v>
       </c>
@@ -7000,7 +6991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
+    <row r="41" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>11</v>
       </c>
@@ -7027,7 +7018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
+    <row r="42" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>11</v>
       </c>
@@ -7054,7 +7045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
+    <row r="43" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>11</v>
       </c>
@@ -7081,7 +7072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
+    <row r="44" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>11</v>
       </c>
@@ -7108,7 +7099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
+    <row r="45" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>11</v>
       </c>
@@ -7135,7 +7126,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
+    <row r="46" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>11</v>
       </c>
@@ -7166,7 +7157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
+    <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>11</v>
       </c>
@@ -7195,7 +7186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
+    <row r="48" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>11</v>
       </c>
@@ -7222,7 +7213,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
+    <row r="49" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>11</v>
       </c>
@@ -7249,7 +7240,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
+    <row r="50" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>11</v>
       </c>
@@ -7282,7 +7273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
+    <row r="51" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>11</v>
       </c>
@@ -7298,9 +7289,6 @@
       <c r="E51" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F51" s="15"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="15"/>
       <c r="I51" s="12"/>
       <c r="J51" s="4" t="s">
         <v>189</v>
@@ -7309,7 +7297,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
+    <row r="52" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>11</v>
       </c>
@@ -7336,7 +7324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
+    <row r="53" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>11</v>
       </c>
@@ -7363,7 +7351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
+    <row r="54" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>11</v>
       </c>
@@ -7390,7 +7378,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
+    <row r="55" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>11</v>
       </c>
@@ -7417,7 +7405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
+    <row r="56" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>11</v>
       </c>
@@ -7444,7 +7432,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
+    <row r="57" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>11</v>
       </c>
@@ -7471,7 +7459,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
+    <row r="58" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>11</v>
       </c>
@@ -7498,7 +7486,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
+    <row r="59" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>11</v>
       </c>
@@ -7525,14 +7513,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
+    <row r="60" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="15" t="s">
         <v>214</v>
       </c>
       <c r="D60" s="10" t="s">
@@ -7552,14 +7540,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
+    <row r="61" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="15" t="s">
         <v>218</v>
       </c>
       <c r="D61" s="10" t="s">
@@ -7579,14 +7567,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
+    <row r="62" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="15" t="s">
         <v>222</v>
       </c>
       <c r="D62" s="10" t="s">
@@ -7606,14 +7594,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
+    <row r="63" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="15" t="s">
         <v>225</v>
       </c>
       <c r="D63" s="10" t="s">
@@ -7633,14 +7621,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+    <row r="64" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="15" t="s">
         <v>228</v>
       </c>
       <c r="D64" s="10" t="s">
@@ -7660,14 +7648,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+    <row r="65" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="15" t="s">
         <v>231</v>
       </c>
       <c r="D65" s="10" t="s">
@@ -7687,20 +7675,20 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
+    <row r="66" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="15" t="s">
         <v>234</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="16" t="s">
         <v>236</v>
       </c>
       <c r="F66" s="11"/>
@@ -7714,14 +7702,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+    <row r="67" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="15" t="s">
         <v>237</v>
       </c>
       <c r="D67" s="10" t="s">
@@ -7745,14 +7733,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+    <row r="68" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C68" s="15" t="s">
         <v>239</v>
       </c>
       <c r="D68" s="10" t="s">
@@ -7774,14 +7762,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+    <row r="69" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="15" t="s">
         <v>242</v>
       </c>
       <c r="D69" s="10" t="s">
@@ -7801,20 +7789,20 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
+    <row r="70" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C70" s="15" t="s">
         <v>245</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E70" s="16" t="s">
         <v>247</v>
       </c>
       <c r="F70" s="11"/>
@@ -7828,14 +7816,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
+    <row r="71" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="C71" s="15" t="s">
         <v>248</v>
       </c>
       <c r="D71" s="10" t="s">
@@ -7844,9 +7832,6 @@
       <c r="E71" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F71" s="15"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="15"/>
       <c r="I71" s="12"/>
       <c r="J71" s="4" t="s">
         <v>189</v>
@@ -7855,14 +7840,14 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
+    <row r="72" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C72" s="15" t="s">
         <v>250</v>
       </c>
       <c r="D72" s="10" t="s">

--- a/src/test/resources/testdata/Modules/10_MyHealthBenefits/MyHealthBenefits/01_MyHealthBenefitsTest.xlsx
+++ b/src/test/resources/testdata/Modules/10_MyHealthBenefits/MyHealthBenefits/01_MyHealthBenefitsTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\10_MyHealthBenefits\MyHealthBenefits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2BF7D8-2C08-47C9-ADC3-BEEE99717A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978B620C-6810-4DEF-A80C-8A578EE90116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="262">
   <si>
     <t>INFLUENCER_ACCOUNT</t>
   </si>
@@ -3272,6 +3272,13 @@
 clickon_teleconsulting_arrow
 clickon_mailicon_try
 verify_welcometomail_text</t>
+  </si>
+  <si>
+    <t>navigatebackto_myhealthpage
+clickon_hospicash_arrow
+clickon_videoicon
+clickon_videoicon
+verify_videoprogressbar_isdisplay</t>
   </si>
 </sst>
 </file>
@@ -4513,7 +4520,7 @@
         <v>101</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>261</v>
       </c>
       <c r="F25" s="21"/>
       <c r="G25" s="21"/>
